--- a/output/monthly_by_game_type.xlsx
+++ b/output/monthly_by_game_type.xlsx
@@ -462,16 +462,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1752</v>
+        <v>1765</v>
       </c>
       <c r="D2" t="n">
-        <v>29672.88986</v>
+        <v>30189.47042</v>
       </c>
       <c r="E2" t="n">
-        <v>15934.25923</v>
+        <v>16712.0551</v>
       </c>
       <c r="F2" t="n">
-        <v>3.748469579207389</v>
+        <v>3.767034044785938</v>
       </c>
     </row>
     <row r="3">
@@ -484,16 +484,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2689</v>
+        <v>2545</v>
       </c>
       <c r="D3" t="n">
-        <v>48892.31051</v>
+        <v>48751.81126</v>
       </c>
       <c r="E3" t="n">
-        <v>26404.90324</v>
+        <v>28256.58096</v>
       </c>
       <c r="F3" t="n">
-        <v>3.752800216232178</v>
+        <v>3.734813013459455</v>
       </c>
     </row>
     <row r="4">
@@ -506,16 +506,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1893</v>
+        <v>1965</v>
       </c>
       <c r="D4" t="n">
-        <v>33141.30939</v>
+        <v>33705.44319</v>
       </c>
       <c r="E4" t="n">
-        <v>20629.17025</v>
+        <v>18459.93602</v>
       </c>
       <c r="F4" t="n">
-        <v>3.599189966051099</v>
+        <v>3.665667039590893</v>
       </c>
     </row>
     <row r="5">
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2859</v>
+        <v>2711</v>
       </c>
       <c r="D5" t="n">
-        <v>51862.29058</v>
+        <v>55352.88483</v>
       </c>
       <c r="E5" t="n">
-        <v>28117.2731</v>
+        <v>31244.6026</v>
       </c>
       <c r="F5" t="n">
-        <v>3.720460175188512</v>
+        <v>3.742219565606926</v>
       </c>
     </row>
     <row r="6">
@@ -550,16 +550,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1847</v>
+        <v>1856</v>
       </c>
       <c r="D6" t="n">
-        <v>33398.37243</v>
+        <v>34184.85392</v>
       </c>
       <c r="E6" t="n">
-        <v>17919.2067</v>
+        <v>20064.67368</v>
       </c>
       <c r="F6" t="n">
-        <v>3.803646129082861</v>
+        <v>3.707095749748835</v>
       </c>
     </row>
     <row r="7">
@@ -572,16 +572,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2769</v>
+        <v>2685</v>
       </c>
       <c r="D7" t="n">
-        <v>50238.6557</v>
+        <v>56809.5264</v>
       </c>
       <c r="E7" t="n">
-        <v>28574.58124</v>
+        <v>32364.62371</v>
       </c>
       <c r="F7" t="n">
-        <v>3.670857807114444</v>
+        <v>3.655820757925258</v>
       </c>
     </row>
     <row r="8">
@@ -594,16 +594,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1911</v>
+        <v>1985</v>
       </c>
       <c r="D8" t="n">
-        <v>33194.70125</v>
+        <v>33100.83504</v>
       </c>
       <c r="E8" t="n">
-        <v>20119.96949</v>
+        <v>18884.54368</v>
       </c>
       <c r="F8" t="n">
-        <v>3.790677439538956</v>
+        <v>3.630144562363548</v>
       </c>
     </row>
     <row r="9">
@@ -616,16 +616,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2799</v>
+        <v>2647</v>
       </c>
       <c r="D9" t="n">
-        <v>52964.92708</v>
+        <v>54855.96467</v>
       </c>
       <c r="E9" t="n">
-        <v>31073.00919</v>
+        <v>31176.75793</v>
       </c>
       <c r="F9" t="n">
-        <v>3.698361417322152</v>
+        <v>3.708169906581464</v>
       </c>
     </row>
     <row r="10">
@@ -638,16 +638,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1861</v>
+        <v>1889</v>
       </c>
       <c r="D10" t="n">
-        <v>29860.92317</v>
+        <v>32265.46173</v>
       </c>
       <c r="E10" t="n">
-        <v>17010.80564</v>
+        <v>18586.71544</v>
       </c>
       <c r="F10" t="n">
-        <v>3.676104896404786</v>
+        <v>3.789186088227679</v>
       </c>
     </row>
     <row r="11">
@@ -660,16 +660,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2684</v>
+        <v>2594</v>
       </c>
       <c r="D11" t="n">
-        <v>49316.60709</v>
+        <v>51128.59607</v>
       </c>
       <c r="E11" t="n">
-        <v>27458.06826</v>
+        <v>28564.54614</v>
       </c>
       <c r="F11" t="n">
-        <v>3.762610405270998</v>
+        <v>3.704827662795059</v>
       </c>
     </row>
     <row r="12">
@@ -682,16 +682,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1891</v>
+        <v>1962</v>
       </c>
       <c r="D12" t="n">
-        <v>34680.12796</v>
+        <v>34428.44385</v>
       </c>
       <c r="E12" t="n">
-        <v>19525.01494</v>
+        <v>18297.50044</v>
       </c>
       <c r="F12" t="n">
-        <v>3.752712760114603</v>
+        <v>3.791025685609559</v>
       </c>
     </row>
     <row r="13">
@@ -704,16 +704,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2835</v>
+        <v>2639</v>
       </c>
       <c r="D13" t="n">
-        <v>51607.43111</v>
+        <v>53403.11068</v>
       </c>
       <c r="E13" t="n">
-        <v>30128.73488</v>
+        <v>29266.60481</v>
       </c>
       <c r="F13" t="n">
-        <v>3.778038227055358</v>
+        <v>3.705287016537975</v>
       </c>
     </row>
     <row r="14">
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1894</v>
+        <v>1945</v>
       </c>
       <c r="D14" t="n">
-        <v>33549.74088</v>
+        <v>34908.60242</v>
       </c>
       <c r="E14" t="n">
-        <v>19232.92063</v>
+        <v>19454.17249</v>
       </c>
       <c r="F14" t="n">
-        <v>3.724101529203562</v>
+        <v>3.846299243888707</v>
       </c>
     </row>
     <row r="15">
@@ -748,16 +748,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2778</v>
+        <v>2705</v>
       </c>
       <c r="D15" t="n">
-        <v>54528.96444</v>
+        <v>55347.36265</v>
       </c>
       <c r="E15" t="n">
-        <v>32165.6536</v>
+        <v>31010.99875</v>
       </c>
       <c r="F15" t="n">
-        <v>3.718466956068284</v>
+        <v>3.649266812795659</v>
       </c>
     </row>
     <row r="16">
@@ -770,16 +770,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1812</v>
+        <v>1854</v>
       </c>
       <c r="D16" t="n">
-        <v>29427.16485</v>
+        <v>32341.79698</v>
       </c>
       <c r="E16" t="n">
-        <v>17716.63692</v>
+        <v>18445.62094</v>
       </c>
       <c r="F16" t="n">
-        <v>3.800011404509912</v>
+        <v>3.622722265558316</v>
       </c>
     </row>
     <row r="17">
@@ -792,16 +792,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2755</v>
+        <v>2553</v>
       </c>
       <c r="D17" t="n">
-        <v>49686.42656</v>
+        <v>52501.17337</v>
       </c>
       <c r="E17" t="n">
-        <v>27273.88791</v>
+        <v>31207.43207</v>
       </c>
       <c r="F17" t="n">
-        <v>3.74189003786223</v>
+        <v>3.753409014899218</v>
       </c>
     </row>
     <row r="18">
@@ -814,16 +814,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1853</v>
+        <v>1938</v>
       </c>
       <c r="D18" t="n">
-        <v>31429.01644</v>
+        <v>33398.0167</v>
       </c>
       <c r="E18" t="n">
-        <v>17898.21266</v>
+        <v>19005.2669</v>
       </c>
       <c r="F18" t="n">
-        <v>3.675023442004062</v>
+        <v>3.689219974831007</v>
       </c>
     </row>
     <row r="19">
@@ -836,16 +836,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2794</v>
+        <v>2636</v>
       </c>
       <c r="D19" t="n">
-        <v>54555.8129</v>
+        <v>54345.57536</v>
       </c>
       <c r="E19" t="n">
-        <v>30239.03491</v>
+        <v>31239.27604</v>
       </c>
       <c r="F19" t="n">
-        <v>3.713729304694492</v>
+        <v>3.707920792801486</v>
       </c>
     </row>
     <row r="20">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1823</v>
+        <v>1888</v>
       </c>
       <c r="D20" t="n">
-        <v>32088.99916</v>
+        <v>31922.74399</v>
       </c>
       <c r="E20" t="n">
-        <v>18073.2337</v>
+        <v>19691.75397</v>
       </c>
       <c r="F20" t="n">
-        <v>3.909529008216237</v>
+        <v>3.887223808142063</v>
       </c>
     </row>
     <row r="21">
@@ -880,16 +880,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2714</v>
+        <v>2606</v>
       </c>
       <c r="D21" t="n">
-        <v>51273.7483</v>
+        <v>52377.03503</v>
       </c>
       <c r="E21" t="n">
-        <v>28252.94179</v>
+        <v>28652.52684</v>
       </c>
       <c r="F21" t="n">
-        <v>3.715561188271297</v>
+        <v>3.782630907496576</v>
       </c>
     </row>
     <row r="22">
@@ -902,16 +902,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1904</v>
+        <v>1956</v>
       </c>
       <c r="D22" t="n">
-        <v>31951.25112</v>
+        <v>33275.11087</v>
       </c>
       <c r="E22" t="n">
-        <v>18230.64119</v>
+        <v>20306.33754</v>
       </c>
       <c r="F22" t="n">
-        <v>3.709095595673021</v>
+        <v>3.859424872476276</v>
       </c>
     </row>
     <row r="23">
@@ -924,16 +924,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2767</v>
+        <v>2614</v>
       </c>
       <c r="D23" t="n">
-        <v>53141.30407</v>
+        <v>51569.52616</v>
       </c>
       <c r="E23" t="n">
-        <v>30207.15774</v>
+        <v>29501.93342</v>
       </c>
       <c r="F23" t="n">
-        <v>3.714583473967136</v>
+        <v>3.835485408337799</v>
       </c>
     </row>
     <row r="24">
@@ -946,16 +946,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1912</v>
+        <v>1925</v>
       </c>
       <c r="D24" t="n">
-        <v>33034.70493</v>
+        <v>36758.3362</v>
       </c>
       <c r="E24" t="n">
-        <v>19467.21119</v>
+        <v>20598.27173</v>
       </c>
       <c r="F24" t="n">
-        <v>3.7394401010008</v>
+        <v>3.805967647391777</v>
       </c>
     </row>
     <row r="25">
@@ -968,16 +968,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2777</v>
+        <v>2685</v>
       </c>
       <c r="D25" t="n">
-        <v>52817.31121</v>
+        <v>56577.28324</v>
       </c>
       <c r="E25" t="n">
-        <v>29826.91448</v>
+        <v>32500.04446</v>
       </c>
       <c r="F25" t="n">
-        <v>3.736340401281326</v>
+        <v>3.784141250676154</v>
       </c>
     </row>
   </sheetData>
